--- a/web/public/forms/orig/o-geomcheuk-sheetpile.xlsx
+++ b/web/public/forms/orig/o-geomcheuk-sheetpile.xlsx
@@ -608,7 +608,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="D1" s="2" t="inlineStr">
@@ -1073,7 +1073,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="D1" s="2" t="inlineStr">
@@ -1454,7 +1454,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="D1" s="20" t="inlineStr">
@@ -1984,7 +1984,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="D1" s="20" t="inlineStr">

--- a/web/public/forms/orig/o-geomcheuk-sheetpile.xlsx
+++ b/web/public/forms/orig/o-geomcheuk-sheetpile.xlsx
@@ -9,14 +9,10 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="검측1" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="검측2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="예시-검측1" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="예시-검측2" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'검측1'!$A$1:$G$24</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'검측2'!$A$1:$G$20</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'예시-검측1'!$A$1:$G$24</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'예시-검측2'!$A$1:$G$20</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -168,7 +164,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -224,9 +220,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -922,25 +915,13 @@
       </c>
       <c r="B19" s="5" t="n"/>
       <c r="C19" s="5" t="n"/>
-      <c r="D19" s="15">
-        <f>COUNTIF(D9:D18,"○")</f>
-        <v/>
-      </c>
-      <c r="E19" s="15">
-        <f>COUNTIF(E9:E18,"○")</f>
-        <v/>
-      </c>
-      <c r="F19" s="16">
-        <f>IF(D19+E19=0,"",IF(E19&gt;0,"불합격 "&amp;E19&amp;"건 — 조치 후 재검측",IF(D19&lt;10,"미확인 "&amp;(10-D19)&amp;"건","전 항목 합격")))</f>
-        <v/>
-      </c>
+      <c r="D19" s="15" t="n"/>
+      <c r="E19" s="15" t="n"/>
+      <c r="F19" s="16" t="n"/>
       <c r="G19" s="5" t="n"/>
     </row>
     <row r="20" ht="17" customHeight="1">
-      <c r="A20" s="17">
-        <f>IF(COUNTIFS(D9:D18,"○",E9:E18,"○")&gt;0,"⚠ 한 항목에 합격·불합격을 함께 표시한 곳이 "&amp;COUNTIFS(D9:D18,"○",E9:E18,"○")&amp;"곳 있습니다.",IF(COUNTIFS(E9:E18,"○",F9:F18,"")&gt;0,"⚠ 불합격 항목 "&amp;COUNTIFS(E9:E18,"○",F9:F18,"")&amp;"건의 조치사항을 적으세요.",""))</f>
-        <v/>
-      </c>
+      <c r="A20" s="17" t="n"/>
     </row>
     <row r="21" ht="6" customHeight="1"/>
     <row r="22" ht="30" customHeight="1">
@@ -994,11 +975,9 @@
       </c>
     </row>
     <row r="24" ht="17" customHeight="1">
-      <c r="A24" s="17">
-        <f>IF(AND(N(C22)&gt;0,N(C23)&gt;0,C23&lt;C22),"⚠ 감리원 검측일이 시공자 점검일보다 빠릅니다 — 날짜를 확인하세요.","")</f>
-        <v/>
-      </c>
-    </row>
+      <c r="A24" s="17" t="n"/>
+    </row>
+    <row r="25"/>
     <row r="26" ht="19.5" customHeight="1">
       <c r="A26" s="19" t="inlineStr">
         <is>
@@ -1306,25 +1285,13 @@
       </c>
       <c r="B15" s="5" t="n"/>
       <c r="C15" s="5" t="n"/>
-      <c r="D15" s="15">
-        <f>COUNTIF(D9:D14,"○")</f>
-        <v/>
-      </c>
-      <c r="E15" s="15">
-        <f>COUNTIF(E9:E14,"○")</f>
-        <v/>
-      </c>
-      <c r="F15" s="16">
-        <f>IF(D15+E15=0,"",IF(E15&gt;0,"불합격 "&amp;E15&amp;"건 — 조치 후 재검측",IF(D15&lt;6,"미확인 "&amp;(6-D15)&amp;"건","전 항목 합격")))</f>
-        <v/>
-      </c>
+      <c r="D15" s="15" t="n"/>
+      <c r="E15" s="15" t="n"/>
+      <c r="F15" s="16" t="n"/>
       <c r="G15" s="5" t="n"/>
     </row>
     <row r="16" ht="17" customHeight="1">
-      <c r="A16" s="17">
-        <f>IF(COUNTIFS(D9:D14,"○",E9:E14,"○")&gt;0,"⚠ 한 항목에 합격·불합격을 함께 표시한 곳이 "&amp;COUNTIFS(D9:D14,"○",E9:E14,"○")&amp;"곳 있습니다.",IF(COUNTIFS(E9:E14,"○",F9:F14,"")&gt;0,"⚠ 불합격 항목 "&amp;COUNTIFS(E9:E14,"○",F9:F14,"")&amp;"건의 조치사항을 적으세요.",""))</f>
-        <v/>
-      </c>
+      <c r="A16" s="17" t="n"/>
     </row>
     <row r="17" ht="6" customHeight="1"/>
     <row r="18" ht="30" customHeight="1">
@@ -1378,970 +1345,13 @@
       </c>
     </row>
     <row r="20" ht="17" customHeight="1">
-      <c r="A20" s="17">
-        <f>IF(AND(N(C18)&gt;0,N(C19)&gt;0,C19&lt;C18),"⚠ 감리원 검측일이 시공자 점검일보다 빠릅니다 — 날짜를 확인하세요.","")</f>
-        <v/>
-      </c>
-    </row>
+      <c r="A20" s="17" t="n"/>
+    </row>
+    <row r="21"/>
     <row r="22" ht="19.5" customHeight="1">
       <c r="A22" s="19" t="inlineStr">
         <is>
           <t>합격·불합격 칸은 목록에서 ○ 를 고르세요(지우려면 Delete). 하늘색 칸 = 자동(건수 · 종합).</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="28">
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="A22:G22"/>
-    <mergeCell ref="A20:G20"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="D1:G1"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="F7:G8"/>
-    <mergeCell ref="A16:G16"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A7:B8"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="F14:G14"/>
-  </mergeCells>
-  <dataValidations count="1">
-    <dataValidation sqref="D9 D10 D11 D12 D13 D14 E9 E10 E11 E12 E13 E14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="목록에서 고르세요" type="list">
-      <formula1>"○"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.5" right="0.5" top="0.45" bottom="0.45" header="0.2" footer="0.2"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00F59E0B"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:G26"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="31" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="6" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
-        </is>
-      </c>
-      <c r="D1" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">작성 예시 (가상의 현장)  </t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="42" customHeight="1">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>검 측  체 크 리 스 트</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="6" customHeight="1"/>
-    <row r="4" ht="28" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>공종 CODE №</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="n"/>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>T-03-02</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>위치 및 부위</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="n"/>
-      <c r="F4" s="7" t="inlineStr">
-        <is>
-          <t>STA.0+120 ~ 0+200 좌측</t>
-        </is>
-      </c>
-      <c r="G4" s="5" t="n"/>
-    </row>
-    <row r="5" ht="28" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>공종(세부공종)</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="n"/>
-      <c r="C5" s="7" t="inlineStr">
-        <is>
-          <t>가시설공(SHEET PILE 타입)</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>공   사   량</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="n"/>
-      <c r="F5" s="7" t="inlineStr">
-        <is>
-          <t>SP-Ⅲ L=10.5m 82매</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="n"/>
-    </row>
-    <row r="6" ht="8" customHeight="1"/>
-    <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>검 사 항 목</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="n"/>
-      <c r="C7" s="9" t="inlineStr">
-        <is>
-          <t>검 사 기 준
-(시방서 또는 도면 등)</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>검 사 결 과</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="8" t="inlineStr">
-        <is>
-          <t>조 치 사 항</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="n"/>
-    </row>
-    <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="5" t="n"/>
-      <c r="B8" s="5" t="n"/>
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>합 격</t>
-        </is>
-      </c>
-      <c r="E8" s="8" t="inlineStr">
-        <is>
-          <t>불합격</t>
-        </is>
-      </c>
-      <c r="F8" s="5" t="n"/>
-      <c r="G8" s="5" t="n"/>
-    </row>
-    <row r="9" ht="40" customHeight="1">
-      <c r="A9" s="10" t="inlineStr">
-        <is>
-          <t>1.</t>
-        </is>
-      </c>
-      <c r="B9" s="11" t="inlineStr">
-        <is>
-          <t>SHEET PILE의 규격확인 및 손상여부(단면 손실 포함)는 점검 하였는가.</t>
-        </is>
-      </c>
-      <c r="C9" s="12" t="inlineStr">
-        <is>
-          <t>육안검사</t>
-        </is>
-      </c>
-      <c r="D9" s="13" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="E9" s="13" t="n"/>
-      <c r="F9" s="7" t="n"/>
-      <c r="G9" s="5" t="n"/>
-    </row>
-    <row r="10" ht="40" customHeight="1">
-      <c r="A10" s="10" t="inlineStr">
-        <is>
-          <t>2.</t>
-        </is>
-      </c>
-      <c r="B10" s="11" t="inlineStr">
-        <is>
-          <t>타입장비는 현장에 적합한가.</t>
-        </is>
-      </c>
-      <c r="C10" s="12" t="inlineStr"/>
-      <c r="D10" s="13" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="E10" s="13" t="n"/>
-      <c r="F10" s="7" t="n"/>
-      <c r="G10" s="5" t="n"/>
-    </row>
-    <row r="11" ht="40" customHeight="1">
-      <c r="A11" s="10" t="inlineStr">
-        <is>
-          <t>3.</t>
-        </is>
-      </c>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t>SHEET PILE 근입 깊이는 적정한가.</t>
-        </is>
-      </c>
-      <c r="C11" s="12" t="inlineStr">
-        <is>
-          <t>설계도면
-구조계산서
-참조</t>
-        </is>
-      </c>
-      <c r="D11" s="13" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="E11" s="13" t="n"/>
-      <c r="F11" s="7" t="n"/>
-      <c r="G11" s="5" t="n"/>
-    </row>
-    <row r="12" ht="40" customHeight="1">
-      <c r="A12" s="10" t="inlineStr">
-        <is>
-          <t>4.</t>
-        </is>
-      </c>
-      <c r="B12" s="11" t="inlineStr">
-        <is>
-          <t>SHEET PILE의 수직도는 적정한가.</t>
-        </is>
-      </c>
-      <c r="C12" s="12" t="inlineStr">
-        <is>
-          <t>1/200이하</t>
-        </is>
-      </c>
-      <c r="D12" s="13" t="n"/>
-      <c r="E12" s="13" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="F12" s="7" t="inlineStr">
-        <is>
-          <t>재타입 후 수직도 1/250 확인(5/8)</t>
-        </is>
-      </c>
-      <c r="G12" s="5" t="n"/>
-    </row>
-    <row r="13" ht="40" customHeight="1">
-      <c r="A13" s="10" t="inlineStr">
-        <is>
-          <t>5.</t>
-        </is>
-      </c>
-      <c r="B13" s="11" t="inlineStr">
-        <is>
-          <t>SHEET PILE 설치시에 인접지반 및 시설물에 피해는 주지않는가.</t>
-        </is>
-      </c>
-      <c r="C13" s="12" t="inlineStr">
-        <is>
-          <t>육안검사</t>
-        </is>
-      </c>
-      <c r="D13" s="13" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="E13" s="13" t="n"/>
-      <c r="F13" s="7" t="n"/>
-      <c r="G13" s="5" t="n"/>
-    </row>
-    <row r="14" ht="40" customHeight="1">
-      <c r="A14" s="10" t="inlineStr">
-        <is>
-          <t>6.</t>
-        </is>
-      </c>
-      <c r="B14" s="11" t="inlineStr">
-        <is>
-          <t>GUIDE BEAM의 규격 및 설치 상태는 설계도면과 일치하는가.</t>
-        </is>
-      </c>
-      <c r="C14" s="12" t="inlineStr">
-        <is>
-          <t>설계도면
-참조</t>
-        </is>
-      </c>
-      <c r="D14" s="13" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="E14" s="13" t="n"/>
-      <c r="F14" s="7" t="n"/>
-      <c r="G14" s="5" t="n"/>
-    </row>
-    <row r="15" ht="40" customHeight="1">
-      <c r="A15" s="10" t="inlineStr">
-        <is>
-          <t>7.</t>
-        </is>
-      </c>
-      <c r="B15" s="11" t="inlineStr">
-        <is>
-          <t>줄파기의 되메우기시에 양질의 토사 사용 여부의 확인.</t>
-        </is>
-      </c>
-      <c r="C15" s="12" t="inlineStr">
-        <is>
-          <t>육안검사</t>
-        </is>
-      </c>
-      <c r="D15" s="13" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="E15" s="13" t="n"/>
-      <c r="F15" s="7" t="n"/>
-      <c r="G15" s="5" t="n"/>
-    </row>
-    <row r="16" ht="40" customHeight="1">
-      <c r="A16" s="10" t="inlineStr">
-        <is>
-          <t>8.</t>
-        </is>
-      </c>
-      <c r="B16" s="11" t="inlineStr">
-        <is>
-          <t>연결부의 이음 상태는 양호한가.</t>
-        </is>
-      </c>
-      <c r="C16" s="12" t="inlineStr">
-        <is>
-          <t>육안검사</t>
-        </is>
-      </c>
-      <c r="D16" s="13" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="E16" s="13" t="n"/>
-      <c r="F16" s="7" t="n"/>
-      <c r="G16" s="5" t="n"/>
-    </row>
-    <row r="17" ht="40" customHeight="1">
-      <c r="A17" s="10" t="inlineStr">
-        <is>
-          <t>9.</t>
-        </is>
-      </c>
-      <c r="B17" s="11" t="inlineStr">
-        <is>
-          <t>근입된 SHEET PILE의 위치 및 선형은 적정한가.</t>
-        </is>
-      </c>
-      <c r="C17" s="12" t="inlineStr">
-        <is>
-          <t>설계도면
-참조</t>
-        </is>
-      </c>
-      <c r="D17" s="13" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="E17" s="13" t="n"/>
-      <c r="F17" s="7" t="n"/>
-      <c r="G17" s="5" t="n"/>
-    </row>
-    <row r="18" ht="40" customHeight="1">
-      <c r="A18" s="10" t="inlineStr">
-        <is>
-          <t>10.</t>
-        </is>
-      </c>
-      <c r="B18" s="11" t="inlineStr">
-        <is>
-          <t>SHEET PILE 이음부의 용접 및 설치상태는 양호한가.</t>
-        </is>
-      </c>
-      <c r="C18" s="12" t="inlineStr">
-        <is>
-          <t>설계도면
-참조</t>
-        </is>
-      </c>
-      <c r="D18" s="13" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="E18" s="13" t="n"/>
-      <c r="F18" s="7" t="n"/>
-      <c r="G18" s="5" t="n"/>
-    </row>
-    <row r="19" ht="26" customHeight="1">
-      <c r="A19" s="14" t="inlineStr">
-        <is>
-          <t>계</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="n"/>
-      <c r="C19" s="5" t="n"/>
-      <c r="D19" s="15">
-        <f>COUNTIF(D9:D18,"○")</f>
-        <v/>
-      </c>
-      <c r="E19" s="15">
-        <f>COUNTIF(E9:E18,"○")</f>
-        <v/>
-      </c>
-      <c r="F19" s="16">
-        <f>IF(D19+E19=0,"",IF(E19&gt;0,"불합격 "&amp;E19&amp;"건 — 조치 후 재검측",IF(D19&lt;10,"미확인 "&amp;(10-D19)&amp;"건","전 항목 합격")))</f>
-        <v/>
-      </c>
-      <c r="G19" s="5" t="n"/>
-    </row>
-    <row r="20" ht="17" customHeight="1">
-      <c r="A20" s="17">
-        <f>IF(COUNTIFS(D9:D18,"○",E9:E18,"○")&gt;0,"⚠ 한 항목에 합격·불합격을 함께 표시한 곳이 "&amp;COUNTIFS(D9:D18,"○",E9:E18,"○")&amp;"곳 있습니다.",IF(COUNTIFS(E9:E18,"○",F9:F18,"")&gt;0,"⚠ 불합격 항목 "&amp;COUNTIFS(E9:E18,"○",F9:F18,"")&amp;"건의 조치사항을 적으세요.",""))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="6" customHeight="1"/>
-    <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>시공자 점검일자</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="n"/>
-      <c r="C22" s="18" t="n">
-        <v>46149</v>
-      </c>
-      <c r="D22" s="4" t="inlineStr">
-        <is>
-          <t>점 검 직 원</t>
-        </is>
-      </c>
-      <c r="E22" s="5" t="n"/>
-      <c r="F22" s="6" t="inlineStr">
-        <is>
-          <t>이공무</t>
-        </is>
-      </c>
-      <c r="G22" s="12" t="inlineStr">
-        <is>
-          <t>(인)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="30" customHeight="1">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>감리원 검측일자</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="n"/>
-      <c r="C23" s="18" t="n">
-        <v>46150</v>
-      </c>
-      <c r="D23" s="4" t="inlineStr">
-        <is>
-          <t>검측감리원</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="n"/>
-      <c r="F23" s="6" t="inlineStr">
-        <is>
-          <t>김감리</t>
-        </is>
-      </c>
-      <c r="G23" s="12" t="inlineStr">
-        <is>
-          <t>(인)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="17" customHeight="1">
-      <c r="A24" s="17">
-        <f>IF(AND(N(C22)&gt;0,N(C23)&gt;0,C23&lt;C22),"⚠ 감리원 검측일이 시공자 점검일보다 빠릅니다 — 날짜를 확인하세요.","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" ht="19.5" customHeight="1">
-      <c r="A26" s="19" t="inlineStr">
-        <is>
-          <t>이 시트는 작성 예시입니다(가상의 공사 · 사람).</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="32">
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="A20:G20"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="A24:G24"/>
-    <mergeCell ref="D1:G1"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="F7:G8"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A7:B8"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="A26:G26"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="F14:G14"/>
-  </mergeCells>
-  <dataValidations count="1">
-    <dataValidation sqref="D9 D10 D11 D12 D13 D14 D15 D16 D17 D18 E9 E10 E11 E12 E13 E14 E15 E16 E17 E18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="목록에서 고르세요" type="list">
-      <formula1>"○"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.5" right="0.5" top="0.45" bottom="0.45" header="0.2" footer="0.2"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00F59E0B"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:G22"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="31" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="6" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
-        </is>
-      </c>
-      <c r="D1" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">작성 예시 (가상의 현장)  </t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="42" customHeight="1">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>검 측  체 크 리 스 트</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="6" customHeight="1"/>
-    <row r="4" ht="28" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>공종 CODE №</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="n"/>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>T-03-03</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>위치 및 부위</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="n"/>
-      <c r="F4" s="7" t="inlineStr">
-        <is>
-          <t>STA.0+120 ~ 0+200 좌측</t>
-        </is>
-      </c>
-      <c r="G4" s="5" t="n"/>
-    </row>
-    <row r="5" ht="28" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>공종(세부공종)</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="n"/>
-      <c r="C5" s="7" t="inlineStr">
-        <is>
-          <t>가시설공(SHEET PILE 연결)</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>공   사   량</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="n"/>
-      <c r="F5" s="7" t="inlineStr">
-        <is>
-          <t>SP-Ⅲ 82매 · HTB 164개</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="n"/>
-    </row>
-    <row r="6" ht="8" customHeight="1"/>
-    <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>검 사 항 목</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="n"/>
-      <c r="C7" s="9" t="inlineStr">
-        <is>
-          <t>검 사 기 준
-(시방서 또는 도면 등)</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>검 사 결 과</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="8" t="inlineStr">
-        <is>
-          <t>조 치 사 항</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="n"/>
-    </row>
-    <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="5" t="n"/>
-      <c r="B8" s="5" t="n"/>
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>합 격</t>
-        </is>
-      </c>
-      <c r="E8" s="8" t="inlineStr">
-        <is>
-          <t>불합격</t>
-        </is>
-      </c>
-      <c r="F8" s="5" t="n"/>
-      <c r="G8" s="5" t="n"/>
-    </row>
-    <row r="9" ht="52" customHeight="1">
-      <c r="A9" s="10" t="inlineStr">
-        <is>
-          <t>1.</t>
-        </is>
-      </c>
-      <c r="B9" s="11" t="inlineStr">
-        <is>
-          <t>SHEET PILE의 규격확인 및 손상여부(단면 손실 포함)는 점검 하였는가.</t>
-        </is>
-      </c>
-      <c r="C9" s="12" t="inlineStr">
-        <is>
-          <t>설계도면 참조
-육안검사</t>
-        </is>
-      </c>
-      <c r="D9" s="13" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="E9" s="13" t="n"/>
-      <c r="F9" s="7" t="n"/>
-      <c r="G9" s="5" t="n"/>
-    </row>
-    <row r="10" ht="52" customHeight="1">
-      <c r="A10" s="10" t="inlineStr">
-        <is>
-          <t>2.</t>
-        </is>
-      </c>
-      <c r="B10" s="11" t="inlineStr">
-        <is>
-          <t>연결부재의 규격 및 손상 여부는 사전에 확인하였는가.</t>
-        </is>
-      </c>
-      <c r="C10" s="12" t="inlineStr">
-        <is>
-          <t>육안검사</t>
-        </is>
-      </c>
-      <c r="D10" s="13" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="E10" s="13" t="n"/>
-      <c r="F10" s="7" t="n"/>
-      <c r="G10" s="5" t="n"/>
-    </row>
-    <row r="11" ht="52" customHeight="1">
-      <c r="A11" s="10" t="inlineStr">
-        <is>
-          <t>3.</t>
-        </is>
-      </c>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t>Bolt 및 Nut의 규격 및 타공 간격은 적합한가.</t>
-        </is>
-      </c>
-      <c r="C11" s="12" t="inlineStr">
-        <is>
-          <t>M22*80(HTB F10T)
-C.T.C 1,000</t>
-        </is>
-      </c>
-      <c r="D11" s="13" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="E11" s="13" t="n"/>
-      <c r="F11" s="7" t="n"/>
-      <c r="G11" s="5" t="n"/>
-    </row>
-    <row r="12" ht="52" customHeight="1">
-      <c r="A12" s="10" t="inlineStr">
-        <is>
-          <t>4.</t>
-        </is>
-      </c>
-      <c r="B12" s="11" t="inlineStr">
-        <is>
-          <t>SHEET PILE 근입깊이는 적정한가.</t>
-        </is>
-      </c>
-      <c r="C12" s="12" t="inlineStr">
-        <is>
-          <t>설계도면
-구조계산서
-참조</t>
-        </is>
-      </c>
-      <c r="D12" s="13" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="E12" s="13" t="n"/>
-      <c r="F12" s="7" t="n"/>
-      <c r="G12" s="5" t="n"/>
-    </row>
-    <row r="13" ht="52" customHeight="1">
-      <c r="A13" s="10" t="inlineStr">
-        <is>
-          <t>5.</t>
-        </is>
-      </c>
-      <c r="B13" s="11" t="inlineStr">
-        <is>
-          <t>SHEET PILE의 수직도는 적정한가.</t>
-        </is>
-      </c>
-      <c r="C13" s="12" t="inlineStr">
-        <is>
-          <t>1/200이하</t>
-        </is>
-      </c>
-      <c r="D13" s="13" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="E13" s="13" t="n"/>
-      <c r="F13" s="7" t="n"/>
-      <c r="G13" s="5" t="n"/>
-    </row>
-    <row r="14" ht="52" customHeight="1">
-      <c r="A14" s="10" t="inlineStr">
-        <is>
-          <t>6.</t>
-        </is>
-      </c>
-      <c r="B14" s="11" t="inlineStr">
-        <is>
-          <t>SHEET PILE 설치시 기시공된 전면부 SHEET PILE, 인접지반, 시설물에 피해는 주지 않는가.</t>
-        </is>
-      </c>
-      <c r="C14" s="12" t="inlineStr">
-        <is>
-          <t>육안검사</t>
-        </is>
-      </c>
-      <c r="D14" s="13" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="E14" s="13" t="n"/>
-      <c r="F14" s="7" t="n"/>
-      <c r="G14" s="5" t="n"/>
-    </row>
-    <row r="15" ht="26" customHeight="1">
-      <c r="A15" s="14" t="inlineStr">
-        <is>
-          <t>계</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="n"/>
-      <c r="C15" s="5" t="n"/>
-      <c r="D15" s="15">
-        <f>COUNTIF(D9:D14,"○")</f>
-        <v/>
-      </c>
-      <c r="E15" s="15">
-        <f>COUNTIF(E9:E14,"○")</f>
-        <v/>
-      </c>
-      <c r="F15" s="16">
-        <f>IF(D15+E15=0,"",IF(E15&gt;0,"불합격 "&amp;E15&amp;"건 — 조치 후 재검측",IF(D15&lt;6,"미확인 "&amp;(6-D15)&amp;"건","전 항목 합격")))</f>
-        <v/>
-      </c>
-      <c r="G15" s="5" t="n"/>
-    </row>
-    <row r="16" ht="17" customHeight="1">
-      <c r="A16" s="17">
-        <f>IF(COUNTIFS(D9:D14,"○",E9:E14,"○")&gt;0,"⚠ 한 항목에 합격·불합격을 함께 표시한 곳이 "&amp;COUNTIFS(D9:D14,"○",E9:E14,"○")&amp;"곳 있습니다.",IF(COUNTIFS(E9:E14,"○",F9:F14,"")&gt;0,"⚠ 불합격 항목 "&amp;COUNTIFS(E9:E14,"○",F9:F14,"")&amp;"건의 조치사항을 적으세요.",""))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="6" customHeight="1"/>
-    <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>시공자 점검일자</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="n"/>
-      <c r="C18" s="18" t="n">
-        <v>46154</v>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>점 검 직 원</t>
-        </is>
-      </c>
-      <c r="E18" s="5" t="n"/>
-      <c r="F18" s="6" t="inlineStr">
-        <is>
-          <t>이공무</t>
-        </is>
-      </c>
-      <c r="G18" s="12" t="inlineStr">
-        <is>
-          <t>(인)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>감리원 검측일자</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="n"/>
-      <c r="C19" s="18" t="n">
-        <v>46154</v>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>검측감리원</t>
-        </is>
-      </c>
-      <c r="E19" s="5" t="n"/>
-      <c r="F19" s="6" t="inlineStr">
-        <is>
-          <t>김감리</t>
-        </is>
-      </c>
-      <c r="G19" s="12" t="inlineStr">
-        <is>
-          <t>(인)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="17" customHeight="1">
-      <c r="A20" s="17">
-        <f>IF(AND(N(C18)&gt;0,N(C19)&gt;0,C19&lt;C18),"⚠ 감리원 검측일이 시공자 점검일보다 빠릅니다 — 날짜를 확인하세요.","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="19.5" customHeight="1">
-      <c r="A22" s="19" t="inlineStr">
-        <is>
-          <t>이 시트는 작성 예시입니다(가상의 공사 · 사람).</t>
         </is>
       </c>
     </row>

--- a/web/public/forms/orig/o-geomcheuk-sheetpile.xlsx
+++ b/web/public/forms/orig/o-geomcheuk-sheetpile.xlsx
@@ -601,7 +601,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="D1" s="2" t="inlineStr">
@@ -1052,7 +1052,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="D1" s="2" t="inlineStr">
